--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20250930_165840.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20250930_165840.xlsx
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20250930_165840.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20250930_165840.xlsx
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
